--- a/data/trans_orig/IQ09_D-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IQ09_D-Provincia-trans_orig.xlsx
@@ -526,7 +526,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Tiempo medio en días que llevan sufriendo esa dolencia, enfermedad o impedimento que le haya limitado de forma continuada (más de 10 días en los últimos 12 meses)</t>
+          <t>Tiempo medio en días que llevan sufriendo esa dolencia, enfermedad o impedimento que le haya limitado de forma continuada (más de 10 días en los últimos 12 meses) (tasa de respuesta: 97,48%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -638,7 +638,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -721,7 +721,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,21; 8,29</t>
+          <t>0,2; 7,97</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -731,7 +731,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,25</t>
+          <t>0,0; 4,3</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -741,7 +741,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,66</t>
+          <t>0,0; 7,63</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -756,29 +756,29 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,48; 18,09</t>
+          <t>1,48; 16,13</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,54; 5,81</t>
+          <t>0,61; 5,82</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,58</t>
+          <t>0,24; 3,54</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,4</t>
+          <t>0,0; 4,18</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -856,17 +856,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,05</t>
+          <t>0,0; 11,92</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,13; 9,01</t>
+          <t>0,13; 8,96</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,9; 13,39</t>
+          <t>0,0; 12,94</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -891,34 +891,34 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,62; 11,21</t>
+          <t>0,71; 11,33</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,29; 8,76</t>
+          <t>0,31; 9,54</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,12; 5,1</t>
+          <t>0,06; 5,05</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,57; 10,07</t>
+          <t>0,58; 10,5</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,21; 9,37</t>
+          <t>1,16; 9,37</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -1036,12 +1036,12 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,9</t>
+          <t>0,0; 8,29</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,49</t>
+          <t>0,0; 6,62</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
@@ -1051,7 +1051,7 @@
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,03</t>
+          <t>0,0; 1,07</t>
         </is>
       </c>
     </row>
@@ -1146,7 +1146,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,08; 1,0</t>
+          <t>0,15; 1,0</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,74</t>
+          <t>0,0; 13,0</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,07; 0,6</t>
+          <t>0,07; 0,61</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,99</t>
+          <t>0,0; 2,42</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1311,17 +1311,17 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,24; 2,06</t>
+          <t>0,24; 1,91</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,32</t>
+          <t>0,0; 14,57</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,77</t>
+          <t>0,0; 1,76</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
@@ -1331,14 +1331,14 @@
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,27; 1,84</t>
+          <t>0,33; 1,91</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1426,7 +1426,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,85</t>
+          <t>0,0; 9,56</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,16; 4,29</t>
+          <t>0,0; 4,35</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -1478,7 +1478,7 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1571,17 +1571,17 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,58; 13,43</t>
+          <t>1,33; 13,26</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,68</t>
+          <t>0,0; 8,18</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,32</t>
+          <t>0,0; 2,31</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -1591,27 +1591,27 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,4; 16,3</t>
+          <t>0,38; 15,39</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,68</t>
+          <t>0,0; 8,18</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,02</t>
+          <t>0,0; 2,95</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,63</t>
+          <t>0,0; 5,64</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>1,85; 12,82</t>
+          <t>1,88; 13,09</t>
         </is>
       </c>
     </row>
@@ -1696,12 +1696,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,55</t>
+          <t>0,0; 5,61</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,93; 14,88</t>
+          <t>1,09; 14,85</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1711,47 +1711,47 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,13; 4,35</t>
+          <t>0,14; 4,82</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,56</t>
+          <t>0,0; 1,67</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,89</t>
+          <t>0,0; 7,85</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,52; 7,39</t>
+          <t>0,5; 7,97</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,85</t>
+          <t>0,0; 3,81</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0,21; 2,46</t>
+          <t>0,21; 2,43</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>0,65; 8,36</t>
+          <t>0,65; 8,82</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>0,34; 5,68</t>
+          <t>0,35; 5,41</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>0,35; 3,09</t>
+          <t>0,37; 2,95</t>
         </is>
       </c>
     </row>
@@ -1836,62 +1836,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1,38; 7,22</t>
+          <t>1,65; 7,4</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1,15; 4,63</t>
+          <t>1,2; 4,67</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,54; 3,96</t>
+          <t>0,53; 3,89</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,56; 3,34</t>
+          <t>0,6; 3,41</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1,6; 5,66</t>
+          <t>1,66; 5,65</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,24; 2,36</t>
+          <t>0,23; 2,51</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,41; 2,95</t>
+          <t>0,42; 3,13</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>1,0; 5,18</t>
+          <t>1,05; 5,35</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1,97; 5,21</t>
+          <t>1,97; 5,13</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>0,94; 2,98</t>
+          <t>0,91; 2,87</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>0,73; 2,76</t>
+          <t>0,71; 2,67</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>1,18; 3,9</t>
+          <t>1,18; 4,17</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ09_D-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IQ09_D-Provincia-trans_orig.xlsx
@@ -721,7 +721,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,2; 7,97</t>
+          <t>0,49; 8,3</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -731,7 +731,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,3</t>
+          <t>0,0; 3,33</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -741,12 +741,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,63</t>
+          <t>0,0; 7,17</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,78</t>
+          <t>0,0; 5,16</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -761,17 +761,17 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,61; 5,82</t>
+          <t>0,52; 5,39</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,24; 3,54</t>
+          <t>0,0; 3,58</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,18</t>
+          <t>0,0; 4,25</t>
         </is>
       </c>
     </row>
@@ -856,17 +856,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,92</t>
+          <t>0,0; 11,49</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,13; 8,96</t>
+          <t>0,13; 8,68</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,94</t>
+          <t>0,0; 13,68</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -891,27 +891,27 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,71; 11,33</t>
+          <t>0,7; 12,62</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,31; 9,54</t>
+          <t>0,29; 9,81</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,06; 5,05</t>
+          <t>0,06; 5,0</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,58; 10,5</t>
+          <t>0,58; 10,22</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,16; 9,37</t>
+          <t>1,21; 9,43</t>
         </is>
       </c>
     </row>
@@ -1051,7 +1051,7 @@
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,07</t>
+          <t>0,0; 0,99</t>
         </is>
       </c>
     </row>
@@ -1176,7 +1176,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,0</t>
+          <t>0,0; 10,74</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,07; 0,61</t>
+          <t>0,07; 0,6</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,42</t>
+          <t>0,0; 2,44</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1316,12 +1316,12 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,57</t>
+          <t>0,0; 15,57</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,76</t>
+          <t>0,0; 1,72</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
@@ -1331,7 +1331,7 @@
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,33; 1,91</t>
+          <t>0,37; 1,97</t>
         </is>
       </c>
     </row>
@@ -1426,7 +1426,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,56</t>
+          <t>0,0; 8,45</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,35</t>
+          <t>0,0; 4,04</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -1561,7 +1561,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,49</t>
+          <t>0,0; 4,47</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1571,17 +1571,17 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,33; 13,26</t>
+          <t>1,46; 11,86</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,18</t>
+          <t>0,0; 8,1</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,31</t>
+          <t>0,0; 2,32</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -1591,27 +1591,27 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,38; 15,39</t>
+          <t>0,45; 15,93</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,18</t>
+          <t>0,0; 8,1</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,95</t>
+          <t>0,0; 3,17</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,64</t>
+          <t>0,0; 5,63</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>1,88; 13,09</t>
+          <t>1,95; 12,63</t>
         </is>
       </c>
     </row>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,61</t>
+          <t>0,0; 5,55</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -1711,47 +1711,47 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,14; 4,82</t>
+          <t>0,13; 4,62</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,67</t>
+          <t>0,0; 1,55</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,85</t>
+          <t>0,0; 7,87</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,5; 7,97</t>
+          <t>0,51; 8,02</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,81</t>
+          <t>0,0; 3,84</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0,21; 2,43</t>
+          <t>0,21; 2,28</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>0,65; 8,82</t>
+          <t>0,54; 8,35</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>0,35; 5,41</t>
+          <t>0,35; 5,7</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>0,37; 2,95</t>
+          <t>0,37; 2,9</t>
         </is>
       </c>
     </row>
@@ -1836,62 +1836,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1,65; 7,4</t>
+          <t>1,52; 7,05</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1,2; 4,67</t>
+          <t>1,15; 4,83</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,53; 3,89</t>
+          <t>0,55; 3,97</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,6; 3,41</t>
+          <t>0,53; 3,55</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1,66; 5,65</t>
+          <t>1,52; 5,45</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,23; 2,51</t>
+          <t>0,3; 2,38</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,42; 3,13</t>
+          <t>0,45; 3,0</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>1,05; 5,35</t>
+          <t>1,18; 5,35</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1,97; 5,13</t>
+          <t>2,02; 5,4</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>0,91; 2,87</t>
+          <t>0,89; 2,94</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>0,71; 2,67</t>
+          <t>0,69; 2,65</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>1,18; 4,17</t>
+          <t>1,13; 3,96</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ09_D-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IQ09_D-Provincia-trans_orig.xlsx
@@ -532,7 +532,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -540,7 +540,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -648,42 +648,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>7,3</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1,9</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>1,68</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>3,18</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>12,0</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>2,68</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0,62</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>7,3</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>1,9</t>
-        </is>
-      </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,68</t>
+          <t>0,0</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>3,32</t>
+          <t>1,41</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>1,21</t>
+          <t>2,08</t>
         </is>
       </c>
     </row>
@@ -716,52 +716,52 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,98; 20,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,49; 8,3</t>
+          <t>0,0; 6,66</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 4,78</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,33</t>
+          <t>0,0; 8,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,98; 20,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,17</t>
+          <t>0,21; 8,29</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,16</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,0</t>
+          <t>0,0; 5,94</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,48; 16,13</t>
+          <t>1,48; 18,09</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,52; 5,39</t>
+          <t>0,54; 5,81</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -771,7 +771,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,25</t>
+          <t>0,0; 5,28</t>
         </is>
       </c>
     </row>
@@ -788,42 +788,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>0,99</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>4,56</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>3,64</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>4,24</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>3,42</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>4,33</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>3,92</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>0,99</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>4,56</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>3,9</t>
+          <t>4,34</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>3,91</t>
+          <t>3,83</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,49</t>
+          <t>0,0; 3,0</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,13; 8,68</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,68</t>
+          <t>0,0; 14,0</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
+          <t>0,57; 10,77</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 12,05</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,13; 9,01</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>0,9; 13,39</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>0,0; 8,0</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 3,0</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 14,0</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>0,7; 12,62</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,29; 9,81</t>
+          <t>0,29; 8,76</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,06; 5,0</t>
+          <t>0,12; 5,1</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,58; 10,22</t>
+          <t>0,57; 10,07</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,21; 9,43</t>
+          <t>1,21; 8,66</t>
         </is>
       </c>
     </row>
@@ -928,42 +928,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>7,45</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
           <t>3,1</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>0,65</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>7,45</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0,0</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>0,67</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>0,22</t>
+          <t>0,26</t>
         </is>
       </c>
     </row>
@@ -996,52 +996,52 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>5,0; 10,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
           <t>0,0; 10,0</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="I9" s="2" t="inlineStr">
         <is>
           <t>0,0; 7,0</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="J9" s="2" t="inlineStr">
         <is>
           <t>0,0; 2,0</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>5,0; 10,0</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,29</t>
+          <t>0,0; 9,9</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,62</t>
+          <t>0,0; 6,49</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
@@ -1051,7 +1051,7 @@
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,99</t>
+          <t>0,0; 1,18</t>
         </is>
       </c>
     </row>
@@ -1068,7 +1068,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>5,16</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -1078,27 +1078,27 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
           <t>0,58</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>5,16</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 13,0</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -1146,7 +1146,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,15; 1,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1166,7 +1166,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,08; 1,0</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1208,12 +1208,12 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>6,36</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>0,48</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -1223,47 +1223,47 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
+          <t>0,85</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>1,0</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>6,36</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>0,48</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>3,66</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>0,41</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>0,86</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>3,66</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>0,41</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>0,88</t>
+          <t>0,87</t>
         </is>
       </c>
     </row>
@@ -1276,12 +1276,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 19,0</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 1,99</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1291,17 +1291,17 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,23; 1,97</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,44</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1311,17 +1311,17 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,24; 1,91</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,57</t>
+          <t>0,0; 14,32</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,72</t>
+          <t>0,0; 1,77</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
@@ -1331,7 +1331,7 @@
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,37; 1,97</t>
+          <t>0,28; 1,82</t>
         </is>
       </c>
     </row>
@@ -1348,42 +1348,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>10,96</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>2,19</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="J14" s="2" t="inlineStr">
         <is>
           <t>—</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1416,29 +1416,29 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
           <t>7,0; 15,0</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 8,45</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
@@ -1446,7 +1446,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 7,85</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,04</t>
+          <t>0,16; 4,29</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -1488,62 +1488,62 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>2,93</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>0,53</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>6,54</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>1,1</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>3,5</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>5,69</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>5,96</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>2,93</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0,53</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>0,85</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>1,41</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>6,36</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>2,93</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>0,85</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>1,41</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>6,15</t>
         </is>
       </c>
     </row>
@@ -1556,52 +1556,52 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 7,68</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,47</t>
+          <t>0,0; 2,32</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>0,38; 16,33</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 4,49</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
           <t>0,0; 7,0</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>1,46; 11,86</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 8,1</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 2,32</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,45; 15,93</t>
+          <t>1,54; 13,7</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,1</t>
+          <t>0,0; 7,68</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,17</t>
+          <t>0,0; 3,02</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>1,95; 12,63</t>
+          <t>1,87; 13,1</t>
         </is>
       </c>
     </row>
@@ -1628,42 +1628,42 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>0,61</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>1,88</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>2,51</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>0,71</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
           <t>1,36</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>5,34</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>1,59</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>0,61</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>1,88</t>
-        </is>
-      </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2,51</t>
+          <t>0,0</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>0,89</t>
+          <t>1,41</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1683,7 +1683,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>1,3</t>
+          <t>1,12</t>
         </is>
       </c>
     </row>
@@ -1696,62 +1696,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>0,0; 1,56</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 7,89</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>0,52; 7,39</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 3,55</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
           <t>0,0; 5,55</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>1,09; 14,85</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>0,13; 4,62</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 1,55</t>
-        </is>
-      </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,87</t>
+          <t>0,93; 14,88</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,51; 8,02</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,84</t>
+          <t>0,11; 4,0</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0,21; 2,28</t>
+          <t>0,21; 2,46</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>0,54; 8,35</t>
+          <t>0,65; 8,36</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>0,35; 5,7</t>
+          <t>0,34; 5,68</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>0,37; 2,9</t>
+          <t>0,27; 2,87</t>
         </is>
       </c>
     </row>
@@ -1768,54 +1768,54 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>3,25</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>0,91</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>1,24</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>2,59</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
           <t>3,68</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>2,58</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>1,64</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>2,06</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>3,41</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
         <is>
           <t>1,66</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>3,25</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>0,91</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>1,24</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>2,57</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>3,41</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>1,66</t>
-        </is>
-      </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
           <t>1,43</t>
@@ -1823,7 +1823,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>2,16</t>
+          <t>2,37</t>
         </is>
       </c>
     </row>
@@ -1836,62 +1836,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1,52; 7,05</t>
+          <t>1,6; 5,66</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1,15; 4,83</t>
+          <t>0,24; 2,36</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,55; 3,97</t>
+          <t>0,41; 2,95</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,53; 3,55</t>
+          <t>0,96; 5,39</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1,52; 5,45</t>
+          <t>1,38; 7,22</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,3; 2,38</t>
+          <t>1,15; 4,63</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,45; 3,0</t>
+          <t>0,54; 3,96</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>1,18; 5,35</t>
+          <t>0,93; 4,39</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>2,02; 5,4</t>
+          <t>1,97; 5,21</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>0,89; 2,94</t>
+          <t>0,94; 2,98</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>0,69; 2,65</t>
+          <t>0,73; 2,76</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>1,13; 3,96</t>
+          <t>1,37; 4,45</t>
         </is>
       </c>
     </row>
